--- a/0_Data/1_Household Data/1_Vietnam/3_Matching_Tables/Item_GTAP_Concordance_Vietnam.xlsx
+++ b/0_Data/1_Household Data/1_Vietnam/3_Matching_Tables/Item_GTAP_Concordance_Vietnam.xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="MATCHING_VIETNAM" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -438,7 +438,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -453,19 +453,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -489,7 +489,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -503,6 +503,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -512,7 +515,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -798,61 +801,64 @@
   <cols>
     <col min="1" max="1" width="11.453125" style="1" customWidth="1"/>
     <col min="2" max="2" width="57.7265625" style="2" customWidth="1"/>
-    <col min="3" max="24" width="7" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="15" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="5" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="24" width="10.90625" style="1" customWidth="1"/>
     <col min="25" max="45" width="0" style="1" hidden="1" customWidth="1"/>
     <col min="46" max="16384" width="10.90625" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:45" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="6"/>
-      <c r="Z1" s="6"/>
-      <c r="AA1" s="6"/>
-      <c r="AB1" s="6"/>
-      <c r="AC1" s="6"/>
-      <c r="AD1" s="6"/>
-      <c r="AE1" s="6"/>
-      <c r="AF1" s="6"/>
-      <c r="AG1" s="6"/>
-      <c r="AH1" s="6"/>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="6"/>
-      <c r="AK1" s="6"/>
-      <c r="AL1" s="6"/>
-      <c r="AM1" s="6"/>
-      <c r="AN1" s="6"/>
-      <c r="AO1" s="6"/>
-      <c r="AP1" s="6"/>
-      <c r="AQ1" s="6"/>
-      <c r="AR1" s="6"/>
-      <c r="AS1" s="6"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
+      <c r="S1" s="7"/>
+      <c r="T1" s="7"/>
+      <c r="U1" s="7"/>
+      <c r="V1" s="7"/>
+      <c r="W1" s="7"/>
+      <c r="X1" s="7"/>
+      <c r="Y1" s="7"/>
+      <c r="Z1" s="7"/>
+      <c r="AA1" s="7"/>
+      <c r="AB1" s="7"/>
+      <c r="AC1" s="7"/>
+      <c r="AD1" s="7"/>
+      <c r="AE1" s="7"/>
+      <c r="AF1" s="7"/>
+      <c r="AG1" s="7"/>
+      <c r="AH1" s="7"/>
+      <c r="AI1" s="7"/>
+      <c r="AJ1" s="7"/>
+      <c r="AK1" s="7"/>
+      <c r="AL1" s="7"/>
+      <c r="AM1" s="7"/>
+      <c r="AN1" s="7"/>
+      <c r="AO1" s="7"/>
+      <c r="AP1" s="7"/>
+      <c r="AQ1" s="7"/>
+      <c r="AR1" s="7"/>
+      <c r="AS1" s="7"/>
     </row>
     <row r="2" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
@@ -861,6 +867,8 @@
       <c r="B2" s="4" t="s">
         <v>132</v>
       </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
@@ -910,9 +918,7 @@
       <c r="B3" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C3">
-        <v>106</v>
-      </c>
+      <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -963,14 +969,24 @@
       <c r="B4" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="3">
         <v>103</v>
       </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
+      <c r="D4" s="3">
+        <v>102</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1011</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1012</v>
+      </c>
+      <c r="G4" s="3">
+        <v>10100</v>
+      </c>
+      <c r="H4" s="3">
+        <v>10200</v>
+      </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
@@ -1016,53 +1032,57 @@
       <c r="B5" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="3">
         <v>104</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="3">
         <v>105</v>
       </c>
-      <c r="E5">
-        <v>122</v>
-      </c>
-      <c r="F5">
+      <c r="E5" s="3">
+        <v>124</v>
+      </c>
+      <c r="F5" s="3">
+        <v>125</v>
+      </c>
+      <c r="G5" s="3">
+        <v>126</v>
+      </c>
+      <c r="H5" s="3">
+        <v>127</v>
+      </c>
+      <c r="I5" s="3">
+        <v>128</v>
+      </c>
+      <c r="J5" s="3">
+        <v>129</v>
+      </c>
+      <c r="K5" s="3">
+        <v>130</v>
+      </c>
+      <c r="L5" s="3">
+        <v>131</v>
+      </c>
+      <c r="M5" s="3">
+        <v>132</v>
+      </c>
+      <c r="N5" s="3">
+        <v>133</v>
+      </c>
+      <c r="O5" s="3">
+        <v>134</v>
+      </c>
+      <c r="P5" s="3">
+        <v>152</v>
+      </c>
+      <c r="Q5" s="3">
         <v>123</v>
       </c>
-      <c r="G5">
-        <v>124</v>
-      </c>
-      <c r="H5">
-        <v>125</v>
-      </c>
-      <c r="I5">
-        <v>126</v>
-      </c>
-      <c r="J5">
-        <v>127</v>
-      </c>
-      <c r="K5">
-        <v>128</v>
-      </c>
-      <c r="L5">
-        <v>129</v>
-      </c>
-      <c r="M5">
-        <v>130</v>
-      </c>
-      <c r="N5">
-        <v>131</v>
-      </c>
-      <c r="O5">
-        <v>132</v>
-      </c>
-      <c r="P5">
-        <v>133</v>
-      </c>
-      <c r="Q5">
-        <v>134</v>
-      </c>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
+      <c r="R5" s="3">
+        <v>12400</v>
+      </c>
+      <c r="S5" s="3">
+        <v>13400</v>
+      </c>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
@@ -1250,16 +1270,18 @@
       <c r="B9" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="3">
+        <v>136</v>
+      </c>
+      <c r="D9" s="3">
+        <v>137</v>
+      </c>
+      <c r="E9" s="3">
         <v>138</v>
       </c>
-      <c r="D9">
-        <v>225</v>
-      </c>
-      <c r="E9">
-        <v>136</v>
-      </c>
-      <c r="F9" s="3"/>
+      <c r="F9" s="3">
+        <v>224</v>
+      </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
@@ -1358,11 +1380,15 @@
       <c r="B11" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="3">
         <v>121</v>
       </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
+      <c r="D11" s="3">
+        <v>1171</v>
+      </c>
+      <c r="E11" s="3">
+        <v>12100</v>
+      </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
@@ -1411,7 +1437,7 @@
       <c r="B12" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="3">
         <v>143</v>
       </c>
       <c r="D12" s="3"/>
@@ -1566,9 +1592,7 @@
       <c r="B15" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C15">
-        <v>118</v>
-      </c>
+      <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
@@ -1619,10 +1643,12 @@
       <c r="B16" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="3">
         <v>202</v>
       </c>
-      <c r="D16" s="3"/>
+      <c r="D16" s="3">
+        <v>203</v>
+      </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
@@ -1723,8 +1749,12 @@
       <c r="B18" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
+      <c r="C18" s="3">
+        <v>208</v>
+      </c>
+      <c r="D18" s="3">
+        <v>209</v>
+      </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
@@ -1825,20 +1855,30 @@
       <c r="B20" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="3">
         <v>111</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="3">
         <v>112</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="3">
+        <v>115</v>
+      </c>
+      <c r="F20" s="3">
         <v>116</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
+      <c r="G20" s="3">
+        <v>11100</v>
+      </c>
+      <c r="H20" s="3">
+        <v>11200</v>
+      </c>
+      <c r="I20" s="3">
+        <v>11500</v>
+      </c>
+      <c r="J20" s="3">
+        <v>11600</v>
+      </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
@@ -1882,20 +1922,24 @@
       <c r="B21" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="3">
         <v>110</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="3">
         <v>113</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="3">
         <v>114</v>
       </c>
-      <c r="F21">
-        <v>115</v>
-      </c>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
+      <c r="F21" s="3">
+        <v>11000</v>
+      </c>
+      <c r="G21" s="3">
+        <v>11300</v>
+      </c>
+      <c r="H21" s="3">
+        <v>11400</v>
+      </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
@@ -1941,8 +1985,8 @@
       <c r="B22" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C22">
-        <v>117</v>
+      <c r="C22" s="3">
+        <v>1172</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
@@ -1994,13 +2038,15 @@
       <c r="B23" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C23">
-        <v>141</v>
-      </c>
-      <c r="D23">
+      <c r="C23" s="3">
+        <v>1411</v>
+      </c>
+      <c r="D23" s="3">
         <v>142</v>
       </c>
-      <c r="E23" s="3"/>
+      <c r="E23" s="3">
+        <v>1412</v>
+      </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
@@ -2049,15 +2095,9 @@
       <c r="B24" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C24">
-        <v>108</v>
-      </c>
-      <c r="D24">
-        <v>101</v>
-      </c>
-      <c r="E24">
-        <v>102</v>
-      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
@@ -2106,10 +2146,12 @@
       <c r="B25" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="3">
         <v>139</v>
       </c>
-      <c r="D25" s="3"/>
+      <c r="D25" s="3">
+        <v>13900</v>
+      </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
@@ -2159,46 +2201,72 @@
       <c r="B26" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="3">
+        <v>106</v>
+      </c>
+      <c r="D26" s="3">
         <v>107</v>
       </c>
-      <c r="D26">
+      <c r="E26" s="3">
+        <v>108</v>
+      </c>
+      <c r="F26" s="3">
         <v>109</v>
       </c>
-      <c r="E26">
+      <c r="G26" s="3">
+        <v>1181</v>
+      </c>
+      <c r="H26" s="3">
         <v>119</v>
       </c>
-      <c r="F26">
+      <c r="I26" s="3">
         <v>120</v>
       </c>
-      <c r="G26">
+      <c r="J26" s="3">
+        <v>122</v>
+      </c>
+      <c r="K26" s="3">
         <v>135</v>
       </c>
-      <c r="H26">
-        <v>137</v>
-      </c>
-      <c r="I26">
+      <c r="L26" s="3">
         <v>140</v>
       </c>
-      <c r="J26">
-        <v>153</v>
-      </c>
-      <c r="K26">
-        <v>154</v>
-      </c>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
-      <c r="R26" s="3"/>
-      <c r="S26" s="3"/>
-      <c r="T26" s="3"/>
-      <c r="U26" s="3"/>
-      <c r="V26" s="3"/>
-      <c r="W26" s="3"/>
-      <c r="X26" s="3"/>
+      <c r="M26" s="3">
+        <v>147</v>
+      </c>
+      <c r="N26" s="3">
+        <v>149</v>
+      </c>
+      <c r="O26" s="3">
+        <v>150</v>
+      </c>
+      <c r="P26" s="3">
+        <v>1182</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>1531</v>
+      </c>
+      <c r="R26" s="3">
+        <v>1532</v>
+      </c>
+      <c r="S26" s="3">
+        <v>1533</v>
+      </c>
+      <c r="T26" s="3">
+        <v>11810</v>
+      </c>
+      <c r="U26" s="3">
+        <v>11820</v>
+      </c>
+      <c r="V26" s="3">
+        <v>12000</v>
+      </c>
+      <c r="W26" s="3">
+        <v>14000</v>
+      </c>
+      <c r="X26" s="3">
+        <v>15000</v>
+      </c>
       <c r="Y26" s="3"/>
       <c r="Z26" s="3"/>
       <c r="AA26" s="3"/>
@@ -2228,34 +2296,36 @@
       <c r="B27" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="3">
         <v>144</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="3">
         <v>145</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="3">
         <v>146</v>
       </c>
-      <c r="F27">
-        <v>147</v>
-      </c>
-      <c r="G27">
+      <c r="F27" s="3">
         <v>148</v>
       </c>
-      <c r="H27">
-        <v>149</v>
-      </c>
-      <c r="I27">
-        <v>150</v>
-      </c>
-      <c r="J27">
+      <c r="G27" s="3">
         <v>151</v>
       </c>
-      <c r="K27">
-        <v>152</v>
-      </c>
-      <c r="L27" s="3"/>
+      <c r="H27" s="3">
+        <v>14400</v>
+      </c>
+      <c r="I27" s="3">
+        <v>14500</v>
+      </c>
+      <c r="J27" s="3">
+        <v>14600</v>
+      </c>
+      <c r="K27" s="3">
+        <v>14800</v>
+      </c>
+      <c r="L27" s="3">
+        <v>15100</v>
+      </c>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
@@ -2297,30 +2367,22 @@
       <c r="B28" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="3">
         <v>301</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="3">
         <v>303</v>
       </c>
-      <c r="E28">
-        <v>304</v>
-      </c>
-      <c r="F28">
+      <c r="E28" s="3">
         <v>305</v>
       </c>
-      <c r="G28">
-        <v>306</v>
-      </c>
-      <c r="H28">
-        <v>314</v>
-      </c>
-      <c r="I28">
+      <c r="F28" s="3">
         <v>316</v>
       </c>
-      <c r="J28">
-        <v>42</v>
-      </c>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
@@ -2364,16 +2426,18 @@
       <c r="B29" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="3">
         <v>302</v>
       </c>
-      <c r="D29">
-        <v>308</v>
-      </c>
-      <c r="E29">
-        <v>309</v>
-      </c>
-      <c r="F29" s="3"/>
+      <c r="D29" s="3">
+        <v>304</v>
+      </c>
+      <c r="E29" s="3">
+        <v>306</v>
+      </c>
+      <c r="F29" s="9">
+        <v>42</v>
+      </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
@@ -2421,8 +2485,12 @@
       <c r="B30" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
+      <c r="C30" s="3">
+        <v>308</v>
+      </c>
+      <c r="D30" s="3">
+        <v>314</v>
+      </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
@@ -2472,12 +2540,8 @@
       <c r="B31" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C31">
-        <v>203</v>
-      </c>
-      <c r="D31">
-        <v>211</v>
-      </c>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
@@ -2527,19 +2591,21 @@
       <c r="B32" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="3">
+        <v>221</v>
+      </c>
+      <c r="D32" s="3">
         <v>222</v>
       </c>
-      <c r="D32">
+      <c r="E32" s="3">
         <v>223</v>
       </c>
-      <c r="E32">
-        <v>224</v>
-      </c>
-      <c r="F32">
+      <c r="F32" s="3">
+        <v>322</v>
+      </c>
+      <c r="G32" s="9">
         <v>43</v>
       </c>
-      <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
@@ -2586,20 +2652,20 @@
       <c r="B33" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="3">
         <v>204</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="3">
         <v>205</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="3">
         <v>206</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="3">
         <v>207</v>
       </c>
-      <c r="G33">
-        <v>209</v>
+      <c r="G33" s="3">
+        <v>212</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
@@ -2647,27 +2713,25 @@
       <c r="B34" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C34">
-        <v>208</v>
-      </c>
-      <c r="D34">
+      <c r="C34" s="3">
+        <v>215</v>
+      </c>
+      <c r="D34" s="3">
         <v>216</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="3">
         <v>217</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="3">
         <v>218</v>
       </c>
-      <c r="G34">
+      <c r="G34" s="3">
         <v>219</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="3">
         <v>220</v>
       </c>
-      <c r="I34">
-        <v>221</v>
-      </c>
+      <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
@@ -2763,8 +2827,12 @@
       <c r="B36" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
+      <c r="C36" s="3">
+        <v>309</v>
+      </c>
+      <c r="D36" s="3">
+        <v>333</v>
+      </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
@@ -2865,8 +2933,12 @@
       <c r="B38" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
+      <c r="C38" s="3">
+        <v>312</v>
+      </c>
+      <c r="D38" s="3">
+        <v>313</v>
+      </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
@@ -3018,42 +3090,38 @@
       <c r="B41" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C41">
-        <v>9</v>
-      </c>
-      <c r="D41">
-        <v>10</v>
-      </c>
-      <c r="E41">
+      <c r="C41" s="3">
         <v>11</v>
       </c>
-      <c r="F41">
+      <c r="D41" s="3">
         <v>12</v>
       </c>
-      <c r="G41">
+      <c r="E41" s="3">
         <v>14</v>
       </c>
-      <c r="H41">
+      <c r="F41" s="3">
         <v>15</v>
       </c>
-      <c r="I41">
+      <c r="G41" s="3">
         <v>16</v>
       </c>
-      <c r="J41">
+      <c r="H41" s="3">
         <v>17</v>
       </c>
-      <c r="K41">
+      <c r="I41" s="3">
         <v>18</v>
       </c>
-      <c r="L41">
+      <c r="J41" s="3">
         <v>19</v>
       </c>
-      <c r="M41">
+      <c r="K41" s="3">
         <v>20</v>
       </c>
-      <c r="N41">
+      <c r="L41" s="3">
         <v>21</v>
       </c>
+      <c r="M41" s="3"/>
+      <c r="N41" s="3"/>
       <c r="O41" s="3"/>
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
@@ -3093,41 +3161,41 @@
       <c r="B42" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C42">
-        <v>7</v>
-      </c>
-      <c r="D42">
+      <c r="C42" s="3">
         <v>13</v>
       </c>
-      <c r="E42">
+      <c r="D42" s="3">
         <v>22</v>
       </c>
-      <c r="F42">
+      <c r="E42" s="3">
         <v>23</v>
       </c>
-      <c r="G42">
+      <c r="F42" s="3">
         <v>24</v>
       </c>
-      <c r="H42">
+      <c r="G42" s="3">
         <v>25</v>
       </c>
-      <c r="I42">
+      <c r="H42" s="3">
         <v>26</v>
       </c>
-      <c r="J42">
+      <c r="I42" s="3">
         <v>27</v>
       </c>
-      <c r="K42">
+      <c r="J42" s="3">
         <v>28</v>
       </c>
-      <c r="L42">
+      <c r="K42" s="3">
+        <v>33</v>
+      </c>
+      <c r="L42" s="3">
         <v>34</v>
       </c>
-      <c r="M42">
-        <v>33</v>
-      </c>
-      <c r="N42">
+      <c r="M42" s="3">
         <v>35</v>
+      </c>
+      <c r="N42" s="3">
+        <v>9</v>
       </c>
       <c r="O42" s="3"/>
       <c r="P42" s="3"/>
@@ -3168,12 +3236,18 @@
       <c r="B43" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="3">
+        <v>310</v>
+      </c>
+      <c r="D43" s="3">
+        <v>315</v>
+      </c>
+      <c r="E43" s="3">
+        <v>7</v>
+      </c>
+      <c r="F43" s="3">
         <v>8</v>
       </c>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
@@ -3221,20 +3295,20 @@
       <c r="B44" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="3">
+        <v>319</v>
+      </c>
+      <c r="D44" s="3">
         <v>1</v>
       </c>
-      <c r="D44">
+      <c r="E44" s="3">
         <v>2</v>
       </c>
-      <c r="E44">
+      <c r="F44" s="3">
         <v>4</v>
       </c>
-      <c r="F44">
+      <c r="G44" s="3">
         <v>5</v>
-      </c>
-      <c r="G44">
-        <v>6</v>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
@@ -3282,13 +3356,13 @@
       <c r="B45" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="3">
         <v>318</v>
       </c>
-      <c r="D45">
-        <v>319</v>
-      </c>
-      <c r="E45">
+      <c r="D45" s="3">
+        <v>6</v>
+      </c>
+      <c r="E45" s="3">
         <v>3</v>
       </c>
       <c r="F45" s="3"/>
@@ -3339,57 +3413,45 @@
       <c r="B46" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C46">
-        <v>215</v>
-      </c>
-      <c r="D46">
-        <v>227</v>
-      </c>
-      <c r="E46">
-        <v>333</v>
-      </c>
-      <c r="F46">
+      <c r="C46" s="3">
+        <v>214</v>
+      </c>
+      <c r="D46" s="3">
+        <v>311</v>
+      </c>
+      <c r="E46" s="3">
         <v>323</v>
       </c>
-      <c r="G46">
+      <c r="F46" s="3">
         <v>324</v>
       </c>
-      <c r="H46">
+      <c r="G46" s="3">
         <v>325</v>
       </c>
-      <c r="I46">
-        <v>322</v>
-      </c>
-      <c r="J46">
-        <v>310</v>
-      </c>
-      <c r="K46">
-        <v>311</v>
-      </c>
-      <c r="L46">
-        <v>312</v>
-      </c>
-      <c r="M46">
-        <v>313</v>
-      </c>
-      <c r="N46">
-        <v>315</v>
-      </c>
-      <c r="O46">
+      <c r="H46" s="3">
         <v>29</v>
       </c>
-      <c r="P46">
+      <c r="I46" s="3">
         <v>30</v>
       </c>
-      <c r="Q46">
+      <c r="J46" s="3">
         <v>31</v>
       </c>
-      <c r="R46">
+      <c r="K46" s="3">
         <v>32</v>
       </c>
-      <c r="S46">
+      <c r="L46" s="3">
+        <v>36</v>
+      </c>
+      <c r="M46" s="9">
         <v>44</v>
       </c>
+      <c r="N46" s="3"/>
+      <c r="O46" s="3"/>
+      <c r="P46" s="3"/>
+      <c r="Q46" s="3"/>
+      <c r="R46" s="3"/>
+      <c r="S46" s="3"/>
       <c r="T46" s="3"/>
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
@@ -3424,7 +3486,7 @@
       <c r="B47" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="3">
         <v>1024</v>
       </c>
       <c r="D47" s="3"/>
@@ -3477,9 +3539,7 @@
       <c r="B48" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C48">
-        <v>210</v>
-      </c>
+      <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
@@ -3530,11 +3590,11 @@
       <c r="B49" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="3">
+        <v>1026</v>
+      </c>
+      <c r="D49" s="3">
         <v>1020</v>
-      </c>
-      <c r="D49">
-        <v>1026</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
@@ -3636,8 +3696,12 @@
       <c r="B51" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
+      <c r="C51" s="3">
+        <v>307</v>
+      </c>
+      <c r="D51" s="3">
+        <v>320</v>
+      </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
@@ -3687,12 +3751,8 @@
       <c r="B52" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C52">
-        <v>331</v>
-      </c>
-      <c r="D52">
-        <v>332</v>
-      </c>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
@@ -3742,7 +3802,7 @@
       <c r="B53" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="3">
         <v>321</v>
       </c>
       <c r="D53" s="3"/>
@@ -3948,13 +4008,13 @@
       <c r="B57" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="3">
         <v>326</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="3">
         <v>327</v>
       </c>
-      <c r="E57">
+      <c r="E57" s="3">
         <v>328</v>
       </c>
       <c r="F57" s="3"/>
@@ -4158,21 +4218,11 @@
       <c r="B61" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C61">
-        <v>228</v>
-      </c>
-      <c r="D61">
-        <v>1014</v>
-      </c>
-      <c r="E61">
-        <v>307</v>
-      </c>
-      <c r="F61">
-        <v>320</v>
-      </c>
-      <c r="G61">
-        <v>400</v>
-      </c>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
       <c r="J61" s="3"/>
@@ -4219,36 +4269,48 @@
       <c r="B62" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C62">
+      <c r="C62" s="3">
+        <v>225</v>
+      </c>
+      <c r="D62" s="3">
+        <v>227</v>
+      </c>
+      <c r="E62" s="3">
+        <v>329</v>
+      </c>
+      <c r="F62" s="3">
+        <v>330</v>
+      </c>
+      <c r="G62" s="3">
+        <v>331</v>
+      </c>
+      <c r="H62" s="3">
+        <v>334</v>
+      </c>
+      <c r="I62" s="3">
+        <v>335</v>
+      </c>
+      <c r="J62" s="3">
         <v>404</v>
       </c>
-      <c r="D62">
+      <c r="K62" s="3">
         <v>405</v>
       </c>
-      <c r="E62">
+      <c r="L62" s="3">
         <v>406</v>
       </c>
-      <c r="F62">
+      <c r="M62" s="3">
         <v>407</v>
       </c>
-      <c r="G62">
-        <v>329</v>
-      </c>
-      <c r="H62">
-        <v>330</v>
-      </c>
-      <c r="I62">
-        <v>334</v>
-      </c>
-      <c r="J62">
-        <v>335</v>
-      </c>
-      <c r="K62" s="3"/>
-      <c r="L62" s="3"/>
-      <c r="M62" s="3"/>
-      <c r="N62" s="3"/>
-      <c r="O62" s="3"/>
-      <c r="P62" s="3"/>
+      <c r="N62" s="3">
+        <v>201</v>
+      </c>
+      <c r="O62" s="3">
+        <v>332</v>
+      </c>
+      <c r="P62" s="3">
+        <v>1014</v>
+      </c>
       <c r="Q62" s="3"/>
       <c r="R62" s="3"/>
       <c r="S62" s="3"/>
@@ -4286,11 +4348,21 @@
       <c r="B63" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C63" s="3"/>
-      <c r="D63" s="3"/>
-      <c r="E63" s="3"/>
-      <c r="F63" s="3"/>
-      <c r="G63" s="3"/>
+      <c r="C63" s="3">
+        <v>213</v>
+      </c>
+      <c r="D63" s="3">
+        <v>401</v>
+      </c>
+      <c r="E63" s="3">
+        <v>402</v>
+      </c>
+      <c r="F63" s="3">
+        <v>403</v>
+      </c>
+      <c r="G63" s="3">
+        <v>400</v>
+      </c>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
       <c r="J63" s="3"/>
@@ -4337,22 +4409,22 @@
       <c r="B64" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="9">
         <v>38</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="9">
         <v>39</v>
       </c>
-      <c r="E64">
+      <c r="E64" s="9">
         <v>40</v>
       </c>
-      <c r="F64">
+      <c r="F64" s="9">
         <v>41</v>
       </c>
-      <c r="G64">
+      <c r="G64" s="9">
         <v>45</v>
       </c>
-      <c r="H64">
+      <c r="H64" s="9">
         <v>46</v>
       </c>
       <c r="I64" s="3"/>
@@ -4451,7 +4523,7 @@
       <c r="B66" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="3">
         <v>1008</v>
       </c>
       <c r="D66" s="3"/>
@@ -4504,42 +4576,40 @@
       <c r="B67" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C67">
-        <v>201</v>
-      </c>
-      <c r="D67">
-        <v>212</v>
-      </c>
-      <c r="E67">
-        <v>213</v>
-      </c>
-      <c r="F67">
-        <v>214</v>
-      </c>
-      <c r="G67">
+      <c r="C67" s="5">
+        <v>154</v>
+      </c>
+      <c r="D67" s="5">
+        <v>228</v>
+      </c>
+      <c r="E67" s="5">
+        <v>317</v>
+      </c>
+      <c r="F67" s="5">
+        <v>336</v>
+      </c>
+      <c r="G67" s="5">
+        <v>408</v>
+      </c>
+      <c r="H67" s="5">
+        <v>15400</v>
+      </c>
+      <c r="I67" s="5">
+        <v>153</v>
+      </c>
+      <c r="J67" s="5">
         <v>226</v>
       </c>
-      <c r="H67">
-        <v>229</v>
-      </c>
-      <c r="I67">
-        <v>401</v>
-      </c>
-      <c r="J67">
-        <v>402</v>
-      </c>
-      <c r="K67">
-        <v>336</v>
-      </c>
-      <c r="L67">
-        <v>408</v>
-      </c>
-      <c r="M67">
-        <v>317</v>
-      </c>
-      <c r="N67">
+      <c r="K67" s="5">
         <v>37</v>
       </c>
+      <c r="L67" s="5">
+        <v>210</v>
+      </c>
+      <c r="M67" s="5">
+        <v>211</v>
+      </c>
+      <c r="N67" s="5"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
@@ -4579,14 +4649,24 @@
       <c r="B68" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C68" s="8">
-        <v>403</v>
-      </c>
-      <c r="D68" s="3"/>
-      <c r="E68" s="3"/>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3"/>
-      <c r="H68" s="3"/>
+      <c r="C68" s="3">
+        <v>101</v>
+      </c>
+      <c r="D68" s="3">
+        <v>117</v>
+      </c>
+      <c r="E68" s="3">
+        <v>118</v>
+      </c>
+      <c r="F68" s="3">
+        <v>141</v>
+      </c>
+      <c r="G68" s="3">
+        <v>11800</v>
+      </c>
+      <c r="H68" s="3">
+        <v>15300</v>
+      </c>
       <c r="I68" s="3"/>
       <c r="J68" s="3"/>
       <c r="K68" s="3"/>
